--- a/data/sources/coho_regulations.xlsx
+++ b/data/sources/coho_regulations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/tyler_garber_dfw_wa_gov/Documents/sport_harvest/sport/sport_harvest_estimator/data/sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DE2489E3-9C7E-4806-A1CE-55F0E427468C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC427FD7-1F0D-4BD1-B83B-52C4753B5C7A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{DE2489E3-9C7E-4806-A1CE-55F0E427468C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30922DF5-0484-4142-9A37-67A8A622B34A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="coho_regulations" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">coho_regulations!$A$1:$E$491</definedName>
   </definedNames>
-  <calcPr calcId="191028" concurrentCalc="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -434,20 +434,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9536AF9F-EFE7-469A-8B3B-7525E4B6BE61}">
-  <sheetPr codeName="Sheet1" filterMode="1">
+  <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:E491"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -481,7 +481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -498,7 +498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -515,7 +515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -532,7 +532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -549,7 +549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -566,7 +566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -583,7 +583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -600,7 +600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -617,7 +617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -634,7 +634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -651,7 +651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -668,7 +668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -685,7 +685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -702,7 +702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -719,7 +719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -736,7 +736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -753,7 +753,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -770,7 +770,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -787,7 +787,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -804,7 +804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -821,7 +821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -838,7 +838,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -855,7 +855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -872,7 +872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -889,7 +889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -906,7 +906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -923,7 +923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -940,7 +940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -957,7 +957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -974,7 +974,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>7</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>7</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>7</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>7</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>7</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>7</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>7</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>7</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>7</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>7</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>7</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>7</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>7</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>7</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>7</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>7</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>7</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>7</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>7</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>7</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>7</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>7</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>7</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>7</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>7</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>7</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>7</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>7</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>7</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>7</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>7</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>7</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>7</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>7</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>7</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>7</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>7</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>7</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>7</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>7</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>7</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>7</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>7</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>7</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>7</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>7</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>7</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>7</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>7</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>5</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>7</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>5</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>7</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>5</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>7</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>7</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>7</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>7</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>7</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>7</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>7</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>7</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>7</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>7</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>7</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>7</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>7</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>7</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>7</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>7</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>5</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>5</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>7</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>7</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>7</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>5</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>7</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>5</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>7</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>7</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>7</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>7</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>7</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>7</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>7</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>7</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>7</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>7</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>7</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>7</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>7</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>5</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>7</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>7</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>7</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>7</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>5</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>5</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>7</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>7</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>7</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>7</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>7</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>7</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>7</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>7</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>7</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>7</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>7</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>7</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>7</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>7</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>5</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>7</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>7</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>7</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>7</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>5</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>5</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>7</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>7</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>7</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>7</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>7</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>7</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>7</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>7</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>7</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>7</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>7</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>7</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>7</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>5</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>5</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>7</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>7</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>7</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>7</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>5</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>7</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>7</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>7</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>5</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>7</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>7</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>7</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>7</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>7</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>7</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>7</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>7</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>7</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>5</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>5</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>7</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>7</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>7</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>5</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>5</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>7</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>7</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>7</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>42261</v>
       </c>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>5</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>7</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>42268</v>
       </c>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>5</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>7</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>42274</v>
       </c>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>5</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>7</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>7</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>5</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>7</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>7</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>7</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>7</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>7</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>7</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>7</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>7</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>7</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>42308</v>
       </c>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>7</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>7</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>5</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>7</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>5</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>7</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>5</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>5</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>7</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>5</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>5</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>5</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>5</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>7</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>5</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>7</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>5</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>5</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>7</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>7</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>7</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>5</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>7</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>7</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>7</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>7</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>7</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>5</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>7</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>7</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>7</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>5</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>5</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>5</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>7</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>5</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>5</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>7</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>7</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>7</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>7</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>7</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>7</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>5</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>7</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>7</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>7</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>7</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>5</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>7</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>7</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>7</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>7</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>5</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>7</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>7</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>7</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>5</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>5</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>5</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>5</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>7</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>5</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>5</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>7</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>7</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>7</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>5</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>5</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>7</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>5</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>5</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>7</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>7</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>5</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>5</v>
       </c>
@@ -7082,7 +7082,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>5</v>
       </c>
@@ -7099,7 +7099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>7</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>5</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>7</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>5</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>7</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>7</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>44530</v>
       </c>
     </row>
-    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>5</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>7</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>7</v>
       </c>
@@ -7246,7 +7246,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>7</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>7</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>7</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>7</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>7</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>7</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>7</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>7</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>7</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>7</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>7</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>7</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>7</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>7</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>7</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>7</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>7</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>7</v>
       </c>
@@ -7552,7 +7552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>7</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>7</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>7</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>5</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>7</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>44714</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>7</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>44715</v>
       </c>
     </row>
-    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>7</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>5</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>5</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>7</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>44743</v>
       </c>
     </row>
-    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>7</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>44834</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>7</v>
       </c>
@@ -7741,7 +7741,7 @@
         <v>44744</v>
       </c>
     </row>
-    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>5</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>7</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>44749</v>
       </c>
     </row>
-    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>5</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>7</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>7</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>44751</v>
       </c>
     </row>
-    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>5</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>5</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>5</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>5</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>5</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>5</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>5</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>5</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>5</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>5</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>5</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>5</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>5</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>5</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>5</v>
       </c>
@@ -8080,7 +8080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>7</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>44834</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>7</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>44777</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>7</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>44778</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>7</v>
       </c>
@@ -8136,7 +8136,7 @@
         <v>44779</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>7</v>
       </c>
@@ -8150,7 +8150,7 @@
         <v>44784</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>7</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>44785</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>7</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>44786</v>
       </c>
     </row>
-    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>5</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>44823</v>
       </c>
     </row>
-    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>5</v>
       </c>
@@ -8209,7 +8209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>7</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>44791</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>7</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>44792</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>7</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>44793</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>7</v>
       </c>
@@ -8265,7 +8265,7 @@
         <v>44794</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>7</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>44798</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>7</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>44799</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>7</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>44800</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>7</v>
       </c>
@@ -8321,7 +8321,7 @@
         <v>44801</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>7</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>44805</v>
       </c>
     </row>
-    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>5</v>
       </c>
@@ -8352,7 +8352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>7</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>44806</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>7</v>
       </c>
@@ -8380,7 +8380,7 @@
         <v>44807</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>7</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>44809</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>7</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>44812</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>7</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>44813</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>7</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>44814</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>7</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>44815</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>7</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>44819</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>7</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>44820</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>7</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>44821</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>7</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>44822</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>7</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>7</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>44827</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>7</v>
       </c>
@@ -8548,7 +8548,7 @@
         <v>44828</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>7</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>44829</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>7</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>44833</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>7</v>
       </c>
@@ -8590,7 +8590,7 @@
         <v>44834</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>7</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>44865</v>
       </c>
     </row>
-    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>7</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>44865</v>
       </c>
     </row>
-    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>5</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>7</v>
       </c>
@@ -8650,16 +8650,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E491" xr:uid="{9536AF9F-EFE7-469A-8B3B-7525E4B6BE61}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="11"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:E448">
-      <sortCondition ref="C264:C491"/>
-    </sortState>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E491">
     <sortCondition ref="C207:C491"/>
   </sortState>
@@ -8683,15 +8673,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE9114A9D0DECB469CD3434F7556ACE4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d7c6d40c49ba7a98dce712687acf420b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="62120a19-a38a-4c78-8e86-03b65bdcf4fa" xmlns:ns3="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f8f7844aaab423fe57564514e62d9bb" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8931,6 +8912,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A00794-6F8A-440F-8D17-1F18CC3F357B}">
   <ds:schemaRefs>
@@ -8944,14 +8934,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{902BFF43-0B71-4183-AE7E-FA994EED3F0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EFEA11F-658A-4460-92CA-EE713A46DF11}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8969,4 +8951,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{902BFF43-0B71-4183-AE7E-FA994EED3F0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/sources/coho_regulations.xlsx
+++ b/data/sources/coho_regulations.xlsx
@@ -8959,4 +8959,10 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{45011977-b912-4387-97a4-f4c94a801377}" enabled="1" method="Standard" siteId="{11d0e217-264e-400a-8ba0-57dcc127d72d}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>